--- a/public/seed/sample-import.xlsx
+++ b/public/seed/sample-import.xlsx
@@ -7,7 +7,8 @@
     <sheet name="Items" sheetId="2" r:id="rId2"/>
     <sheet name="Customers" sheetId="3" r:id="rId3"/>
     <sheet name="Opening stock" sheetId="4" r:id="rId4"/>
-    <sheet name="Rates" sheetId="5" r:id="rId5"/>
+    <sheet name="Recipes" sheetId="5" r:id="rId5"/>
+    <sheet name="Rates" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -968,6 +969,145 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F6"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Product code</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Pieces per plate</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Ingredient code</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Qty per plate</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Recipe name</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>320</v>
+      </c>
+      <c r="C2" t="str">
+        <v>RM-BESAN</v>
+      </c>
+      <c r="D2">
+        <v>12</v>
+      </c>
+      <c r="E2" t="str">
+        <v>KG</v>
+      </c>
+      <c r="F2" t="str">
+        <v>MYSORE PAK PLATE</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>8</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v>RM-SUGAR</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3" t="str">
+        <v>KG</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>8</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v>RM-GHEE</v>
+      </c>
+      <c r="D4">
+        <v>500</v>
+      </c>
+      <c r="E4" t="str">
+        <v>G</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>480</v>
+      </c>
+      <c r="C5" t="str">
+        <v>RM-BESAN</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5" t="str">
+        <v>KG</v>
+      </c>
+      <c r="F5" t="str">
+        <v>BOONDI LADDU PLATE</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>12</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v>RM-SUGAR</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6" t="str">
+        <v>KG</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
